--- a/forms/trg/Formulir_TRG_fis-rg.xlsx
+++ b/forms/trg/Formulir_TRG_fis-rg.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. dr. Annisa Anwar Muthaher, SH, M.Kes, Sp.FM, MH</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -1112,7 +1116,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1145,7 +1149,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
